--- a/cve/webchess-cve.xlsx
+++ b/cve/webchess-cve.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,11 +462,11 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CVE-2019-20896</t>
+          <t>CVE-2023-39851</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,85 +481,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['mainmenu.php']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['to']</t>
+          <t>['playerID']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>WebChess 1.0 allows SQL injection via the messageFrom, gameID, opponent, messageID, or to parameter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CVE-2023-22959</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SQL Injection</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>['0.9.0', '1.0.0']</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>['mainmenu.php', 'chess.php', 'opponentspassword.php']</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>WebChess through 0.9.0 and 1.0.0.rc2 allows SQL injection: mainmenu.php, chess.php, and opponentspassword.php (txtFirstName, txtLastName).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CVE-2023-39851</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SQL Injection</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>['1.0']</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>['mainmenu.php']</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>['$playerID']</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
         <is>
           <t>webchess v1.0 was discovered to contain a SQL injection vulnerability via the $playerID parameter at mainmenu.php. NOTE: this is disputed by a third party who indicates that the playerID is a session variable controlled by the server, and thus cannot be used for exploitation.</t>
         </is>
